--- a/backend/financialdata.xlsx
+++ b/backend/financialdata.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN227"/>
+  <dimension ref="A1:AP227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -617,6 +617,16 @@
           <t>fiftyTwoWeekHigh</t>
         </is>
       </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>Distress_Label</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>Regime_Label</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -734,6 +744,12 @@
       </c>
       <c r="AN2" t="n">
         <v>93.95245130287273</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -853,6 +869,12 @@
       <c r="AN3" t="n">
         <v>378.0532256184443</v>
       </c>
+      <c r="AO3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -977,6 +999,12 @@
       <c r="AN4" t="n">
         <v>413.6541708039877</v>
       </c>
+      <c r="AO4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1097,6 +1125,12 @@
       <c r="AN5" t="n">
         <v>157.8028508001376</v>
       </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1221,6 +1255,12 @@
       <c r="AN6" t="n">
         <v>158.8335309052032</v>
       </c>
+      <c r="AO6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1339,6 +1379,12 @@
       <c r="AN7" t="n">
         <v>226.8939761000422</v>
       </c>
+      <c r="AO7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1463,6 +1509,12 @@
       <c r="AN8" t="n">
         <v>383.345877989392</v>
       </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1585,6 +1637,12 @@
       <c r="AN9" t="n">
         <v>336.843455674193</v>
       </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1709,6 +1767,12 @@
       <c r="AN10" t="n">
         <v>263.0622968512546</v>
       </c>
+      <c r="AO10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1833,6 +1897,12 @@
       <c r="AN11" t="n">
         <v>176.83464864803</v>
       </c>
+      <c r="AO11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1959,6 +2029,12 @@
       <c r="AN12" t="n">
         <v>197.8990454164622</v>
       </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2080,6 +2156,12 @@
       </c>
       <c r="AN13" t="n">
         <v>271.6812969308866</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -2203,6 +2285,12 @@
       <c r="AN14" t="n">
         <v>134.6545218756926</v>
       </c>
+      <c r="AO14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2325,6 +2413,12 @@
       <c r="AN15" t="n">
         <v>499.8729529787587</v>
       </c>
+      <c r="AO15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2446,6 +2540,12 @@
       </c>
       <c r="AN16" t="n">
         <v>206.7149601604852</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -2563,6 +2663,12 @@
       <c r="AN17" t="n">
         <v>213.921437471634</v>
       </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2682,6 +2788,12 @@
       </c>
       <c r="AN18" t="n">
         <v>450.7372763329527</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2797,6 +2909,12 @@
       <c r="AN19" t="n">
         <v>350.8894489659939</v>
       </c>
+      <c r="AO19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2913,6 +3031,12 @@
       <c r="AN20" t="n">
         <v>131.5548797745471</v>
       </c>
+      <c r="AO20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3035,6 +3159,12 @@
       <c r="AN21" t="n">
         <v>404.8687450510388</v>
       </c>
+      <c r="AO21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3157,6 +3287,12 @@
       <c r="AN22" t="n">
         <v>304.309932615144</v>
       </c>
+      <c r="AO22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3279,6 +3415,12 @@
       <c r="AN23" t="n">
         <v>238.5164522770466</v>
       </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3393,6 +3535,12 @@
       <c r="AN24" t="n">
         <v>233.9303769941434</v>
       </c>
+      <c r="AO24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3513,6 +3661,12 @@
       <c r="AN25" t="n">
         <v>170.6286383702943</v>
       </c>
+      <c r="AO25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3634,6 +3788,12 @@
       </c>
       <c r="AN26" t="n">
         <v>318.8358959766387</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -3755,6 +3915,12 @@
       <c r="AN27" t="n">
         <v>245.6723023716858</v>
       </c>
+      <c r="AO27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3879,6 +4045,12 @@
       <c r="AN28" t="n">
         <v>263.3963974958587</v>
       </c>
+      <c r="AO28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4005,6 +4177,12 @@
       <c r="AN29" t="n">
         <v>237.9950519753002</v>
       </c>
+      <c r="AO29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4125,6 +4303,12 @@
       <c r="AN30" t="n">
         <v>486.0961835633651</v>
       </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4242,6 +4426,12 @@
       </c>
       <c r="AN31" t="n">
         <v>316.5835030967829</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -4361,6 +4551,12 @@
       <c r="AN32" t="n">
         <v>98.14128747213128</v>
       </c>
+      <c r="AO32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4485,6 +4681,12 @@
       <c r="AN33" t="n">
         <v>149.3463257549422</v>
       </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4611,6 +4813,12 @@
       <c r="AN34" t="n">
         <v>106.3336064911477</v>
       </c>
+      <c r="AO34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4735,6 +4943,12 @@
       <c r="AN35" t="n">
         <v>109.7220893193772</v>
       </c>
+      <c r="AO35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4861,6 +5075,12 @@
       <c r="AN36" t="n">
         <v>274.1880724039125</v>
       </c>
+      <c r="AO36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4983,6 +5203,12 @@
         <v>1.931649929364177</v>
       </c>
       <c r="AN37" t="inlineStr"/>
+      <c r="AO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -5103,6 +5329,12 @@
       <c r="AN38" t="n">
         <v>263.5838940874162</v>
       </c>
+      <c r="AO38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5224,6 +5456,12 @@
       </c>
       <c r="AN39" t="n">
         <v>249.687598687057</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -5335,6 +5573,12 @@
       <c r="AN40" t="n">
         <v>104.0940749167738</v>
       </c>
+      <c r="AO40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -5457,6 +5701,12 @@
       <c r="AN41" t="n">
         <v>467.165545158338</v>
       </c>
+      <c r="AO41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -5577,6 +5827,12 @@
       <c r="AN42" t="n">
         <v>234.9628114130171</v>
       </c>
+      <c r="AO42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -5701,6 +5957,12 @@
       <c r="AN43" t="n">
         <v>310.2741126528841</v>
       </c>
+      <c r="AO43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -5819,6 +6081,12 @@
       <c r="AN44" t="n">
         <v>407.9524823553782</v>
       </c>
+      <c r="AO44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5941,6 +6209,12 @@
       <c r="AN45" t="n">
         <v>445.0884442002813</v>
       </c>
+      <c r="AO45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -6057,6 +6331,12 @@
       <c r="AN46" t="n">
         <v>342.590491579169</v>
       </c>
+      <c r="AO46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6181,6 +6461,12 @@
       <c r="AN47" t="n">
         <v>166.9159439352654</v>
       </c>
+      <c r="AO47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -6303,6 +6589,12 @@
       <c r="AN48" t="n">
         <v>452.8029833179414</v>
       </c>
+      <c r="AO48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -6425,6 +6717,12 @@
       <c r="AN49" t="n">
         <v>398.5852012870046</v>
       </c>
+      <c r="AO49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP49" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6547,6 +6845,12 @@
       <c r="AN50" t="n">
         <v>345.2728269564822</v>
       </c>
+      <c r="AO50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP50" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -6671,6 +6975,12 @@
       <c r="AN51" t="n">
         <v>402.7063030184287</v>
       </c>
+      <c r="AO51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP51" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -6793,6 +7103,12 @@
       <c r="AN52" t="n">
         <v>421.2722345810279</v>
       </c>
+      <c r="AO52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP52" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -6915,6 +7231,12 @@
       <c r="AN53" t="n">
         <v>473.3056603019032</v>
       </c>
+      <c r="AO53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP53" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -7039,6 +7361,12 @@
       <c r="AN54" t="n">
         <v>112.6604170029178</v>
       </c>
+      <c r="AO54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP54" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -7161,6 +7489,12 @@
       <c r="AN55" t="n">
         <v>268.1133292085211</v>
       </c>
+      <c r="AO55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -7284,6 +7618,12 @@
       </c>
       <c r="AN56" t="n">
         <v>221.189003378403</v>
+      </c>
+      <c r="AO56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP56" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -7399,6 +7739,12 @@
       <c r="AN57" t="n">
         <v>124.6797028831032</v>
       </c>
+      <c r="AO57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP57" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -7518,6 +7864,12 @@
       </c>
       <c r="AN58" t="n">
         <v>490.5972221068195</v>
+      </c>
+      <c r="AO58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP58" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -7637,6 +7989,12 @@
       <c r="AN59" t="n">
         <v>68.91110382713238</v>
       </c>
+      <c r="AO59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP59" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -7759,6 +8117,12 @@
       <c r="AN60" t="n">
         <v>65.60162002691749</v>
       </c>
+      <c r="AO60" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP60" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -7877,6 +8241,12 @@
       <c r="AN61" t="n">
         <v>81.91949726019804</v>
       </c>
+      <c r="AO61" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP61" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -7997,6 +8367,12 @@
       <c r="AN62" t="n">
         <v>227.5592340189409</v>
       </c>
+      <c r="AO62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP62" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -8121,6 +8497,12 @@
       <c r="AN63" t="n">
         <v>104.2512873816606</v>
       </c>
+      <c r="AO63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP63" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -8235,6 +8617,12 @@
       <c r="AN64" t="n">
         <v>114.1673648368589</v>
       </c>
+      <c r="AO64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP64" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -8359,6 +8747,12 @@
       <c r="AN65" t="n">
         <v>422.0183118836694</v>
       </c>
+      <c r="AO65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP65" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -8483,6 +8877,12 @@
       <c r="AN66" t="n">
         <v>294.3610627809484</v>
       </c>
+      <c r="AO66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP66" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -8607,6 +9007,12 @@
       <c r="AN67" t="n">
         <v>247.6174174851867</v>
       </c>
+      <c r="AO67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP67" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -8733,6 +9139,12 @@
       <c r="AN68" t="n">
         <v>269.4325143502449</v>
       </c>
+      <c r="AO68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP68" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -8853,6 +9265,12 @@
       <c r="AN69" t="n">
         <v>252.2073839178389</v>
       </c>
+      <c r="AO69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP69" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -8973,6 +9391,12 @@
       <c r="AN70" t="n">
         <v>451.3424651648306</v>
       </c>
+      <c r="AO70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP70" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -9093,6 +9517,12 @@
       <c r="AN71" t="n">
         <v>345.8090669765579</v>
       </c>
+      <c r="AO71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP71" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -9214,6 +9644,12 @@
       </c>
       <c r="AN72" t="n">
         <v>190.3387360625974</v>
+      </c>
+      <c r="AO72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP72" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -9331,6 +9767,12 @@
       <c r="AN73" t="n">
         <v>403.3352944167838</v>
       </c>
+      <c r="AO73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP73" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -9453,6 +9895,12 @@
       <c r="AN74" t="n">
         <v>256.8491916811976</v>
       </c>
+      <c r="AO74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP74" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -9573,6 +10021,12 @@
         <v>0.9946806316381667</v>
       </c>
       <c r="AN75" t="inlineStr"/>
+      <c r="AO75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP75" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -9693,6 +10147,12 @@
       <c r="AN76" t="n">
         <v>211.3603076861929</v>
       </c>
+      <c r="AO76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP76" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -9813,6 +10273,12 @@
       <c r="AN77" t="n">
         <v>234.2354323176583</v>
       </c>
+      <c r="AO77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP77" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -9935,6 +10401,12 @@
       <c r="AN78" t="n">
         <v>455.8730885371175</v>
       </c>
+      <c r="AO78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP78" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -10057,6 +10529,12 @@
       <c r="AN79" t="n">
         <v>490.3364607751133</v>
       </c>
+      <c r="AO79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP79" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -10174,6 +10652,12 @@
       </c>
       <c r="AN80" t="n">
         <v>408.5066287361175</v>
+      </c>
+      <c r="AO80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP80" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -10291,6 +10775,12 @@
       <c r="AN81" t="n">
         <v>283.4154474712677</v>
       </c>
+      <c r="AO81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP81" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -10409,6 +10899,12 @@
       <c r="AN82" t="n">
         <v>97.65761198169093</v>
       </c>
+      <c r="AO82" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP82" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -10529,6 +11025,12 @@
       <c r="AN83" t="n">
         <v>444.8615209945169</v>
       </c>
+      <c r="AO83" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP83" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -10647,6 +11149,12 @@
       <c r="AN84" t="n">
         <v>242.4206001665018</v>
       </c>
+      <c r="AO84" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP84" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -10769,6 +11277,12 @@
       <c r="AN85" t="n">
         <v>461.2047997429667</v>
       </c>
+      <c r="AO85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP85" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -10893,6 +11407,12 @@
       <c r="AN86" t="n">
         <v>150.0625871366766</v>
       </c>
+      <c r="AO86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP86" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -11015,6 +11535,12 @@
       <c r="AN87" t="n">
         <v>302.3052327225275</v>
       </c>
+      <c r="AO87" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP87" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -11133,6 +11659,12 @@
       <c r="AN88" t="n">
         <v>207.7342404287728</v>
       </c>
+      <c r="AO88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP88" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -11252,6 +11784,12 @@
       </c>
       <c r="AN89" t="n">
         <v>120.4145222016203</v>
+      </c>
+      <c r="AO89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP89" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="90">
@@ -11371,6 +11909,12 @@
       <c r="AN90" t="n">
         <v>244.5558018815063</v>
       </c>
+      <c r="AO90" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP90" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -11493,6 +12037,12 @@
       <c r="AN91" t="n">
         <v>56.47165073243826</v>
       </c>
+      <c r="AO91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP91" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -11609,6 +12159,12 @@
       <c r="AN92" t="n">
         <v>360.8977894478703</v>
       </c>
+      <c r="AO92" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP92" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -11729,6 +12285,12 @@
       <c r="AN93" t="n">
         <v>145.0543241628189</v>
       </c>
+      <c r="AO93" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP93" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -11845,6 +12407,12 @@
       <c r="AN94" t="n">
         <v>184.7225181674067</v>
       </c>
+      <c r="AO94" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP94" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -11964,6 +12532,12 @@
       <c r="AM95" t="inlineStr"/>
       <c r="AN95" t="n">
         <v>292.1102174137563</v>
+      </c>
+      <c r="AO95" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP95" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -12083,6 +12657,12 @@
       <c r="AN96" t="n">
         <v>486.4669364053359</v>
       </c>
+      <c r="AO96" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP96" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -12201,6 +12781,12 @@
       <c r="AN97" t="n">
         <v>243.4933463544769</v>
       </c>
+      <c r="AO97" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP97" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -12320,6 +12906,12 @@
       </c>
       <c r="AN98" t="n">
         <v>304.6016996784484</v>
+      </c>
+      <c r="AO98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP98" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -12433,6 +13025,12 @@
       <c r="AN99" t="n">
         <v>133.5798824023335</v>
       </c>
+      <c r="AO99" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP99" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -12557,6 +13155,12 @@
       <c r="AN100" t="n">
         <v>380.7166313277024</v>
       </c>
+      <c r="AO100" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP100" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -12683,6 +13287,12 @@
       <c r="AN101" t="n">
         <v>305.5884337922362</v>
       </c>
+      <c r="AO101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP101" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -12807,6 +13417,12 @@
       <c r="AN102" t="n">
         <v>103.3896945837111</v>
       </c>
+      <c r="AO102" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP102" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -12931,6 +13547,12 @@
       <c r="AN103" t="n">
         <v>238.6322941559546</v>
       </c>
+      <c r="AO103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP103" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -13053,6 +13675,12 @@
       <c r="AN104" t="n">
         <v>490.2596541755855</v>
       </c>
+      <c r="AO104" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP104" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -13171,6 +13799,12 @@
       </c>
       <c r="AM105" t="inlineStr"/>
       <c r="AN105" t="inlineStr"/>
+      <c r="AO105" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP105" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -13291,6 +13925,12 @@
       <c r="AN106" t="n">
         <v>441.8098049558477</v>
       </c>
+      <c r="AO106" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP106" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -13405,6 +14045,12 @@
       <c r="AN107" t="n">
         <v>120.3426368189874</v>
       </c>
+      <c r="AO107" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP107" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -13526,6 +14172,12 @@
       </c>
       <c r="AN108" t="n">
         <v>96.27916647086451</v>
+      </c>
+      <c r="AO108" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP108" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="109">
@@ -13643,6 +14295,12 @@
       <c r="AN109" t="n">
         <v>128.5912336533483</v>
       </c>
+      <c r="AO109" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP109" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -13765,6 +14423,12 @@
       <c r="AN110" t="n">
         <v>110.5593201968485</v>
       </c>
+      <c r="AO110" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP110" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -13887,6 +14551,12 @@
       <c r="AN111" t="n">
         <v>187.584780851281</v>
       </c>
+      <c r="AO111" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP111" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -14011,6 +14681,12 @@
       <c r="AN112" t="n">
         <v>274.158474596619</v>
       </c>
+      <c r="AO112" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP112" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -14131,6 +14807,12 @@
       <c r="AN113" t="n">
         <v>346.1459981254214</v>
       </c>
+      <c r="AO113" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP113" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -14256,6 +14938,12 @@
       </c>
       <c r="AN114" t="n">
         <v>458.6083454397481</v>
+      </c>
+      <c r="AO114" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP114" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -14377,6 +15065,12 @@
         <v>1.060669505102825</v>
       </c>
       <c r="AN115" t="inlineStr"/>
+      <c r="AO115" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP115" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -14495,6 +15189,12 @@
       <c r="AN116" t="n">
         <v>133.0065729769475</v>
       </c>
+      <c r="AO116" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP116" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -14615,6 +15315,12 @@
       <c r="AN117" t="n">
         <v>114.150449764902</v>
       </c>
+      <c r="AO117" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -14738,6 +15444,12 @@
       </c>
       <c r="AN118" t="n">
         <v>490.1993008369512</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -14855,6 +15567,12 @@
       <c r="AN119" t="n">
         <v>306.6291224291257</v>
       </c>
+      <c r="AO119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -14979,6 +15697,12 @@
       <c r="AN120" t="n">
         <v>309.7026870745579</v>
       </c>
+      <c r="AO120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -15103,6 +15827,12 @@
       <c r="AN121" t="n">
         <v>498.6272378352513</v>
       </c>
+      <c r="AO121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -15223,6 +15953,12 @@
       <c r="AN122" t="n">
         <v>154.5011109056044</v>
       </c>
+      <c r="AO122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -15344,6 +16080,12 @@
       </c>
       <c r="AN123" t="n">
         <v>478.5740385794261</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="124">
@@ -15461,6 +16203,12 @@
       <c r="AN124" t="n">
         <v>100.6657099381375</v>
       </c>
+      <c r="AO124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -15587,6 +16335,12 @@
       <c r="AN125" t="n">
         <v>256.1128774627409</v>
       </c>
+      <c r="AO125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -15711,6 +16465,12 @@
       <c r="AN126" t="n">
         <v>411.0808030030959</v>
       </c>
+      <c r="AO126" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -15831,6 +16591,12 @@
       <c r="AN127" t="n">
         <v>457.384549554732</v>
       </c>
+      <c r="AO127" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -15955,6 +16721,12 @@
       <c r="AN128" t="n">
         <v>121.9458935148986</v>
       </c>
+      <c r="AO128" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -16077,6 +16849,12 @@
       <c r="AN129" t="n">
         <v>200.6550688508056</v>
       </c>
+      <c r="AO129" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -16195,6 +16973,12 @@
       <c r="AN130" t="n">
         <v>267.7370984889401</v>
       </c>
+      <c r="AO130" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -16317,6 +17101,12 @@
       <c r="AN131" t="n">
         <v>415.3130232578989</v>
       </c>
+      <c r="AO131" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -16437,6 +17227,12 @@
       <c r="AN132" t="n">
         <v>142.6910161446328</v>
       </c>
+      <c r="AO132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -16555,6 +17351,12 @@
       <c r="AN133" t="n">
         <v>145.2856379235888</v>
       </c>
+      <c r="AO133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -16679,6 +17481,12 @@
       <c r="AN134" t="n">
         <v>88.23483045025989</v>
       </c>
+      <c r="AO134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -16798,6 +17606,12 @@
       <c r="AM135" t="inlineStr"/>
       <c r="AN135" t="n">
         <v>73.73477847299782</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="136">
@@ -16919,6 +17733,12 @@
       <c r="AN136" t="n">
         <v>433.4217871121118</v>
       </c>
+      <c r="AO136" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -17043,6 +17863,12 @@
       <c r="AN137" t="n">
         <v>108.6589085194695</v>
       </c>
+      <c r="AO137" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -17167,6 +17993,12 @@
       <c r="AN138" t="n">
         <v>219.7408021059374</v>
       </c>
+      <c r="AO138" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -17288,6 +18120,12 @@
       </c>
       <c r="AN139" t="n">
         <v>459.4685711718734</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="140">
@@ -17409,6 +18247,12 @@
       <c r="AN140" t="n">
         <v>268.3537050944103</v>
       </c>
+      <c r="AO140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -17525,6 +18369,12 @@
       <c r="AN141" t="n">
         <v>310.9233092214762</v>
       </c>
+      <c r="AO141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -17647,6 +18497,12 @@
       <c r="AN142" t="n">
         <v>489.8554534327291</v>
       </c>
+      <c r="AO142" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -17767,6 +18623,12 @@
       <c r="AN143" t="n">
         <v>217.4196055154933</v>
       </c>
+      <c r="AO143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -17893,6 +18755,12 @@
       <c r="AN144" t="n">
         <v>78.84261996627896</v>
       </c>
+      <c r="AO144" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP144" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -18013,6 +18881,12 @@
       <c r="AN145" t="n">
         <v>190.775388885899</v>
       </c>
+      <c r="AO145" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP145" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -18131,6 +19005,12 @@
       <c r="AN146" t="n">
         <v>258.7934378481714</v>
       </c>
+      <c r="AO146" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP146" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -18251,6 +19131,12 @@
       <c r="AN147" t="n">
         <v>72.1890441994211</v>
       </c>
+      <c r="AO147" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP147" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -18372,6 +19258,12 @@
       </c>
       <c r="AN148" t="n">
         <v>74.795690821474</v>
+      </c>
+      <c r="AO148" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP148" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="149">
@@ -18486,6 +19378,12 @@
       </c>
       <c r="AN149" t="n">
         <v>392.0157058114282</v>
+      </c>
+      <c r="AO149" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP149" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="150">
@@ -18603,6 +19501,12 @@
       <c r="AN150" t="n">
         <v>97.54265545201882</v>
       </c>
+      <c r="AO150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP150" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -18725,6 +19629,12 @@
         <v>2.468178927933028</v>
       </c>
       <c r="AN151" t="inlineStr"/>
+      <c r="AO151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP151" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -18846,6 +19756,12 @@
       </c>
       <c r="AN152" t="n">
         <v>169.7456158417889</v>
+      </c>
+      <c r="AO152" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP152" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="153">
@@ -18965,6 +19881,12 @@
       <c r="AN153" t="n">
         <v>218.8946055978562</v>
       </c>
+      <c r="AO153" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP153" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -19081,6 +20003,12 @@
       <c r="AN154" t="n">
         <v>176.6647861029137</v>
       </c>
+      <c r="AO154" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP154" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -19199,6 +20127,12 @@
       <c r="AN155" t="n">
         <v>481.8855746578861</v>
       </c>
+      <c r="AO155" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP155" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -19324,6 +20258,12 @@
       </c>
       <c r="AN156" t="n">
         <v>253.0085314090286</v>
+      </c>
+      <c r="AO156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP156" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="157">
@@ -19445,6 +20385,12 @@
       <c r="AN157" t="n">
         <v>353.0388780101447</v>
       </c>
+      <c r="AO157" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP157" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -19569,6 +20515,12 @@
       <c r="AN158" t="n">
         <v>453.8895469349378</v>
       </c>
+      <c r="AO158" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP158" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -19689,6 +20641,12 @@
       <c r="AN159" t="n">
         <v>325.9023075811587</v>
       </c>
+      <c r="AO159" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP159" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -19808,6 +20766,12 @@
       </c>
       <c r="AN160" t="n">
         <v>107.1997208901608</v>
+      </c>
+      <c r="AO160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP160" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="161">
@@ -19927,6 +20891,12 @@
       <c r="AN161" t="n">
         <v>210.4515145295999</v>
       </c>
+      <c r="AO161" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP161" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -20049,6 +21019,12 @@
       <c r="AN162" t="n">
         <v>495.10639359893</v>
       </c>
+      <c r="AO162" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP162" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -20171,6 +21147,12 @@
       <c r="AN163" t="n">
         <v>64.61184726128673</v>
       </c>
+      <c r="AO163" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP163" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -20295,6 +21277,12 @@
       <c r="AN164" t="n">
         <v>471.8665275795971</v>
       </c>
+      <c r="AO164" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP164" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -20421,6 +21409,12 @@
       <c r="AN165" t="n">
         <v>460.103817297384</v>
       </c>
+      <c r="AO165" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP165" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -20545,6 +21539,12 @@
       <c r="AN166" t="n">
         <v>337.2009867682751</v>
       </c>
+      <c r="AO166" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP166" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -20663,6 +21663,12 @@
       <c r="AN167" t="n">
         <v>215.303231874776</v>
       </c>
+      <c r="AO167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP167" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -20785,6 +21791,12 @@
       <c r="AN168" t="n">
         <v>82.88829096176761</v>
       </c>
+      <c r="AO168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP168" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -20905,6 +21917,12 @@
       <c r="AN169" t="n">
         <v>160.99540108015</v>
       </c>
+      <c r="AO169" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP169" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -21023,6 +22041,12 @@
       <c r="AN170" t="n">
         <v>259.3748890741655</v>
       </c>
+      <c r="AO170" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP170" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -21143,6 +22167,12 @@
       <c r="AN171" t="n">
         <v>206.279813437564</v>
       </c>
+      <c r="AO171" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP171" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -21265,6 +22295,12 @@
       <c r="AN172" t="n">
         <v>61.62753749900504</v>
       </c>
+      <c r="AO172" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP172" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -21384,6 +22420,12 @@
       </c>
       <c r="AN173" t="n">
         <v>162.6614283068849</v>
+      </c>
+      <c r="AO173" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP173" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="174">
@@ -21499,6 +22541,12 @@
       <c r="AN174" t="n">
         <v>446.5661304933552</v>
       </c>
+      <c r="AO174" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP174" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -21620,6 +22668,12 @@
       </c>
       <c r="AN175" t="n">
         <v>393.8430139604957</v>
+      </c>
+      <c r="AO175" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP175" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="176">
@@ -21737,6 +22791,12 @@
       <c r="AN176" t="n">
         <v>436.5412462049991</v>
       </c>
+      <c r="AO176" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP176" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -21855,6 +22915,12 @@
       <c r="AN177" t="n">
         <v>208.2694180814637</v>
       </c>
+      <c r="AO177" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP177" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -21979,6 +23045,12 @@
       <c r="AN178" t="n">
         <v>90.34350405605555</v>
       </c>
+      <c r="AO178" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP178" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -22103,6 +23175,12 @@
       <c r="AN179" t="n">
         <v>178.3339682045215</v>
       </c>
+      <c r="AO179" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP179" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -22225,6 +23303,12 @@
       <c r="AN180" t="n">
         <v>99.74442483886124</v>
       </c>
+      <c r="AO180" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP180" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -22346,6 +23430,12 @@
       </c>
       <c r="AN181" t="n">
         <v>485.6099774205824</v>
+      </c>
+      <c r="AO181" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP181" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="182">
@@ -22459,6 +23549,12 @@
       <c r="AN182" t="n">
         <v>135.9975302110152</v>
       </c>
+      <c r="AO182" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP182" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -22577,6 +23673,12 @@
       <c r="AN183" t="n">
         <v>127.7407932264893</v>
       </c>
+      <c r="AO183" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP183" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -22699,6 +23801,12 @@
       <c r="AN184" t="n">
         <v>53.19343962269923</v>
       </c>
+      <c r="AO184" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP184" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -22815,6 +23923,12 @@
       <c r="AN185" t="n">
         <v>158.320663548578</v>
       </c>
+      <c r="AO185" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP185" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -22939,6 +24053,12 @@
       <c r="AN186" t="n">
         <v>118.5026962625901</v>
       </c>
+      <c r="AO186" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP186" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -23053,6 +24173,12 @@
       <c r="AN187" t="n">
         <v>273.9047375249266</v>
       </c>
+      <c r="AO187" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP187" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -23177,6 +24303,12 @@
       <c r="AN188" t="n">
         <v>80.14599247813142</v>
       </c>
+      <c r="AO188" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP188" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -23301,6 +24433,12 @@
       <c r="AN189" t="n">
         <v>169.1673448002435</v>
       </c>
+      <c r="AO189" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP189" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -23422,6 +24560,12 @@
       </c>
       <c r="AN190" t="n">
         <v>234.3024172681292</v>
+      </c>
+      <c r="AO190" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP190" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="191">
@@ -23541,6 +24685,12 @@
       <c r="AN191" t="n">
         <v>460.51455249552</v>
       </c>
+      <c r="AO191" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP191" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -23658,6 +24808,12 @@
       <c r="AM192" t="inlineStr"/>
       <c r="AN192" t="n">
         <v>69.74648976593463</v>
+      </c>
+      <c r="AO192" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP192" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="193">
@@ -23781,6 +24937,12 @@
       <c r="AN193" t="n">
         <v>490.2194585882633</v>
       </c>
+      <c r="AO193" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP193" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -23905,6 +25067,12 @@
       <c r="AN194" t="n">
         <v>283.3218387240082</v>
       </c>
+      <c r="AO194" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP194" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -24029,6 +25197,12 @@
       <c r="AN195" t="n">
         <v>334.97101280187</v>
       </c>
+      <c r="AO195" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP195" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -24147,6 +25321,12 @@
       <c r="AN196" t="n">
         <v>318.7024790069765</v>
       </c>
+      <c r="AO196" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP196" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -24271,6 +25451,12 @@
       <c r="AN197" t="n">
         <v>165.2095278776809</v>
       </c>
+      <c r="AO197" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP197" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -24391,6 +25577,12 @@
       <c r="AN198" t="n">
         <v>355.3970422221037</v>
       </c>
+      <c r="AO198" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP198" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -24513,6 +25705,12 @@
       <c r="AN199" t="n">
         <v>377.8768205567496</v>
       </c>
+      <c r="AO199" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP199" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -24633,6 +25831,12 @@
       <c r="AN200" t="n">
         <v>348.7062307736498</v>
       </c>
+      <c r="AO200" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP200" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -24754,6 +25958,12 @@
       </c>
       <c r="AN201" t="n">
         <v>176.4832484503009</v>
+      </c>
+      <c r="AO201" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP201" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="202">
@@ -24873,6 +26083,12 @@
       <c r="AN202" t="n">
         <v>330.4914951915759</v>
       </c>
+      <c r="AO202" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP202" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -24994,6 +26210,12 @@
       </c>
       <c r="AN203" t="n">
         <v>310.0446866484091</v>
+      </c>
+      <c r="AO203" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP203" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="204">
@@ -25111,6 +26333,12 @@
       <c r="AN204" t="n">
         <v>251.2728356707049</v>
       </c>
+      <c r="AO204" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP204" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -25229,6 +26457,12 @@
       <c r="AN205" t="n">
         <v>359.6529466428576</v>
       </c>
+      <c r="AO205" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP205" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -25348,6 +26582,12 @@
       <c r="AM206" t="inlineStr"/>
       <c r="AN206" t="n">
         <v>311.6412026910892</v>
+      </c>
+      <c r="AO206" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP206" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="207">
@@ -25471,6 +26711,12 @@
       <c r="AN207" t="n">
         <v>201.1757690205202</v>
       </c>
+      <c r="AO207" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP207" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -25597,6 +26843,12 @@
       <c r="AN208" t="n">
         <v>487.9151201421089</v>
       </c>
+      <c r="AO208" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP208" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -25723,6 +26975,12 @@
       <c r="AN209" t="n">
         <v>411.4098900213107</v>
       </c>
+      <c r="AO209" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP209" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -25841,6 +27099,12 @@
       <c r="AN210" t="n">
         <v>338.4527257943155</v>
       </c>
+      <c r="AO210" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP210" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -25961,6 +27225,12 @@
       <c r="AN211" t="n">
         <v>369.1313167074821</v>
       </c>
+      <c r="AO211" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP211" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -26081,6 +27351,12 @@
       <c r="AN212" t="n">
         <v>327.9771158278074</v>
       </c>
+      <c r="AO212" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP212" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -26205,6 +27481,12 @@
       <c r="AN213" t="n">
         <v>228.9357435797389</v>
       </c>
+      <c r="AO213" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP213" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -26329,6 +27611,12 @@
       <c r="AN214" t="n">
         <v>489.2352496126335</v>
       </c>
+      <c r="AO214" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP214" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -26455,6 +27743,12 @@
       <c r="AN215" t="n">
         <v>323.8572169282884</v>
       </c>
+      <c r="AO215" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP215" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -26579,6 +27873,12 @@
       <c r="AN216" t="n">
         <v>137.6572111897671</v>
       </c>
+      <c r="AO216" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP216" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -26699,6 +27999,12 @@
       <c r="AN217" t="n">
         <v>76.34147003602256</v>
       </c>
+      <c r="AO217" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP217" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -26821,6 +28127,12 @@
       <c r="AN218" t="n">
         <v>351.2354289141396</v>
       </c>
+      <c r="AO218" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP218" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -26937,6 +28249,12 @@
       <c r="AN219" t="n">
         <v>198.220130165398</v>
       </c>
+      <c r="AO219" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP219" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -27057,6 +28375,12 @@
       <c r="AN220" t="n">
         <v>363.2996462545726</v>
       </c>
+      <c r="AO220" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP220" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -27179,6 +28503,12 @@
       <c r="AN221" t="n">
         <v>121.3412713249656</v>
       </c>
+      <c r="AO221" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP221" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -27294,6 +28624,12 @@
       </c>
       <c r="AN222" t="n">
         <v>252.4607514884774</v>
+      </c>
+      <c r="AO222" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP222" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="223">
@@ -27411,6 +28747,12 @@
       <c r="AN223" t="n">
         <v>161.0363393003214</v>
       </c>
+      <c r="AO223" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP223" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -27533,6 +28875,12 @@
         <v>1.387199402636374</v>
       </c>
       <c r="AN224" t="inlineStr"/>
+      <c r="AO224" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP224" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -27653,6 +29001,12 @@
       <c r="AN225" t="n">
         <v>343.2559076952921</v>
       </c>
+      <c r="AO225" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP225" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -27771,6 +29125,12 @@
         <v>1.276242913536994</v>
       </c>
       <c r="AN226" t="inlineStr"/>
+      <c r="AO226" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP226" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -27888,6 +29248,12 @@
       </c>
       <c r="AN227" t="n">
         <v>393.2595737941124</v>
+      </c>
+      <c r="AO227" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP227" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
